--- a/Costos.xlsx
+++ b/Costos.xlsx
@@ -2,6 +2,7 @@
 <file path=word/document.xml><?xml version="1.0" encoding="utf-8"?>
 <w:document xmlns:wpc="http://schemas.microsoft.com/office/word/2010/wordprocessingCanvas" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" xmlns:cx3="http://schemas.microsoft.com/office/drawing/2016/5/9/chartex" xmlns:cx4="http://schemas.microsoft.com/office/drawing/2016/5/10/chartex" xmlns:cx5="http://schemas.microsoft.com/office/drawing/2016/5/11/chartex" xmlns:cx6="http://schemas.microsoft.com/office/drawing/2016/5/12/chartex" xmlns:cx7="http://schemas.microsoft.com/office/drawing/2016/5/13/chartex" xmlns:cx8="http://schemas.microsoft.com/office/drawing/2016/5/14/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:aink="http://schemas.microsoft.com/office/drawing/2016/ink" xmlns:am3d="http://schemas.microsoft.com/office/drawing/2017/model3d" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:oel="http://schemas.microsoft.com/office/2019/extlst" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:wp14="http://schemas.microsoft.com/office/word/2010/wordprocessingDrawing" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:w16cex="http://schemas.microsoft.com/office/word/2018/wordml/cex" xmlns:w16cid="http://schemas.microsoft.com/office/word/2016/wordml/cid" xmlns:w16="http://schemas.microsoft.com/office/word/2018/wordml" xmlns:w16du="http://schemas.microsoft.com/office/word/2023/wordml/word16du" xmlns:w16sdtdh="http://schemas.microsoft.com/office/word/2020/wordml/sdtdatahash" xmlns:w16sdtfl="http://schemas.microsoft.com/office/word/2024/wordml/sdtformatlock" xmlns:w16se="http://schemas.microsoft.com/office/word/2015/wordml/symex" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wpi="http://schemas.microsoft.com/office/word/2010/wordprocessingInk" xmlns:wne="http://schemas.microsoft.com/office/word/2006/wordml" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" mc:Ignorable="w14 w15 w16se w16cid w16 w16cex w16sdtdh w16sdtfl w16du wp14">
   <w:body>
+    <w:p/>
     <w:p>
       <w:r>
         <w:t xml:space="preserve">Quizá es el tema más constante en la literatura, el cine y el arte en general, y el sentimiento más deseado en nuestras vidas. Todos alguna vez lo hemos sentido, gozado y </w:t>
@@ -50,11 +51,11 @@
     </w:p>
     <w:p>
       <w:r>
-        <w:t xml:space="preserve">La primera fase de una relación amorosa es el enamoramiento, el cual es transitorio, dominado por procesos de atracción y que inicia por la percepción y el consecuente placer producido por la estimulación de nuestros sentidos. Antiguamente el estímulo más importante (quizá lo siga siendo) en una relación amorosa, y que generó por </w:t>
+        <w:t xml:space="preserve">La primera fase de una relación amorosa es el enamoramiento, el cual es transitorio, dominado por procesos de atracción y que inicia por la percepción y el consecuente placer producido por la estimulación de nuestros sentidos. Antiguamente el estímulo </w:t>
       </w:r>
       <w:r>
         <w:lastRenderedPageBreak/>
-        <w:t>mucho tiempo la frase "amor a primera vista", era justamente la vista, dada la importancia que ha adquirido para nosotros este sentido a lo largo de la evolución, sin hacer menos la estimulación del oído, el olfato, el gusto y el tacto. Sin embargo, en estos tiempos modernos los avances en la comunicación han hecho que muchas veces el primer contacto entre dos personas sea virtual, a través del correo electrónico o las redes sociales, y que sin tener una estimulación olfativa, auditiva o incluso visual se pueda desencadenar el enamoramiento.</w:t>
+        <w:t>más importante (quizá lo siga siendo) en una relación amorosa, y que generó por mucho tiempo la frase "amor a primera vista", era justamente la vista, dada la importancia que ha adquirido para nosotros este sentido a lo largo de la evolución, sin hacer menos la estimulación del oído, el olfato, el gusto y el tacto. Sin embargo, en estos tiempos modernos los avances en la comunicación han hecho que muchas veces el primer contacto entre dos personas sea virtual, a través del correo electrónico o las redes sociales, y que sin tener una estimulación olfativa, auditiva o incluso visual se pueda desencadenar el enamoramiento.</w:t>
       </w:r>
     </w:p>
     <w:p>
@@ -704,6 +705,7 @@
   <w:style w:type="character" w:default="1" w:styleId="Fuentedeprrafopredeter">
     <w:name w:val="Default Paragraph Font"/>
     <w:uiPriority w:val="1"/>
+    <w:semiHidden/>
     <w:unhideWhenUsed/>
   </w:style>
   <w:style w:type="table" w:default="1" w:styleId="Tablanormal">
